--- a/data/trans_dic/IP26C_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 18,83</t>
+          <t>8,57; 19,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 12,11</t>
+          <t>3,2; 12,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 15,25</t>
+          <t>5,23; 15,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 13,49</t>
+          <t>4,66; 13,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 16,04</t>
+          <t>6,09; 16,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 15,65</t>
+          <t>5,77; 15,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 14,9</t>
+          <t>4,65; 14,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,97; 20,85</t>
+          <t>8,66; 20,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,25; 15,75</t>
+          <t>8,54; 15,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 12,41</t>
+          <t>5,36; 12,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,1; 12,81</t>
+          <t>5,95; 12,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,0; 15,86</t>
+          <t>8,12; 15,48</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 15,64</t>
+          <t>4,93; 16,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,53; 20,41</t>
+          <t>8,34; 20,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 14,62</t>
+          <t>5,83; 14,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 16,21</t>
+          <t>5,13; 15,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 11,44</t>
+          <t>3,03; 11,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 16,54</t>
+          <t>5,78; 16,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 14,06</t>
+          <t>4,88; 14,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 15,98</t>
+          <t>5,43; 15,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 12,04</t>
+          <t>4,87; 11,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 16,57</t>
+          <t>8,59; 16,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 12,24</t>
+          <t>6,16; 12,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 14,11</t>
+          <t>6,68; 13,72</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,68; 21,05</t>
+          <t>7,49; 22,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 17,01</t>
+          <t>5,92; 17,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 16,09</t>
+          <t>4,21; 16,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 16,36</t>
+          <t>3,45; 16,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,55; 20,19</t>
+          <t>9,05; 19,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 15,8</t>
+          <t>6,09; 16,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 18,44</t>
+          <t>6,49; 18,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,18; 28,17</t>
+          <t>10,14; 27,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,72; 18,22</t>
+          <t>9,85; 18,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 14,12</t>
+          <t>7,01; 14,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 14,94</t>
+          <t>6,7; 15,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 19,68</t>
+          <t>8,34; 19,28</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 12,94</t>
+          <t>6,63; 13,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 11,57</t>
+          <t>5,07; 11,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 14,33</t>
+          <t>7,18; 13,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 11,32</t>
+          <t>4,62; 11,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,79; 16,1</t>
+          <t>8,62; 15,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 14,23</t>
+          <t>7,25; 13,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,38; 13,03</t>
+          <t>6,84; 13,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,3</t>
+          <t>4,1; 10,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,69; 13,76</t>
+          <t>8,51; 13,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 11,36</t>
+          <t>7,07; 11,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,76; 12,46</t>
+          <t>7,91; 12,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 10,06</t>
+          <t>5,26; 9,97</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 19,29</t>
+          <t>7,73; 18,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 16,38</t>
+          <t>7,17; 15,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 11,93</t>
+          <t>4,3; 11,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 18,56</t>
+          <t>9,04; 19,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,54</t>
+          <t>2,18; 8,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,69; 17,55</t>
+          <t>7,96; 17,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 13,26</t>
+          <t>5,17; 12,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,75; 15,23</t>
+          <t>5,91; 15,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,26</t>
+          <t>5,5; 11,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,13; 15,06</t>
+          <t>9,27; 15,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 11,04</t>
+          <t>5,59; 10,74</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,26; 15,23</t>
+          <t>8,36; 15,22</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,14; 23,65</t>
+          <t>10,35; 23,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,77; 28,18</t>
+          <t>10,02; 28,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,37; 18,82</t>
+          <t>5,98; 19,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,2; 10,0</t>
+          <t>2,09; 9,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,85</t>
+          <t>2,8; 12,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,05; 25,06</t>
+          <t>10,57; 25,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 13,81</t>
+          <t>2,7; 15,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,95; 28,72</t>
+          <t>10,11; 28,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,76; 16,34</t>
+          <t>7,6; 16,36</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,78; 23,72</t>
+          <t>12,83; 24,18</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,71; 13,24</t>
+          <t>5,02; 13,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,55; 17,3</t>
+          <t>7,52; 17,63</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,57; 13,79</t>
+          <t>9,73; 13,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,59; 12,32</t>
+          <t>8,41; 12,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,6; 11,38</t>
+          <t>7,52; 11,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,15; 11,07</t>
+          <t>7,13; 11,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,58</t>
+          <t>7,81; 11,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,37; 13,39</t>
+          <t>9,46; 13,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 10,94</t>
+          <t>7,27; 10,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,2; 13,36</t>
+          <t>9,1; 13,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,17; 11,83</t>
+          <t>9,2; 11,91</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,4; 12,28</t>
+          <t>9,45; 12,25</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,84; 10,54</t>
+          <t>7,99; 10,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,83; 11,63</t>
+          <t>8,74; 11,55</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>13374</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5634</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7703</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8656</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10152</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8700</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8592</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>18560</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>23526</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14334</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16294</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>27216</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>8882; 19782</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2816; 10696</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4305; 12410</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4812; 13670</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5936; 15985</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5145; 13997</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4644; 14129</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>11852; 27891</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>17191; 31848</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9494; 22010</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10845; 23577</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>19493; 37173</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8285</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12628</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9718</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5276</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10340</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9353</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>9259</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>13561</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>22968</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>19070</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>18466</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4281; 14017</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7652; 18381</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6091; 15503</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4858; 14699</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2585; 9740</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5555; 16018</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5432; 15989</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>5190; 15252</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>8370; 19792</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>16142; 30375</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>13303; 27035</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>12708; 26103</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8837</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8800</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5395</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4476</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13754</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8602</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>8789</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>10902</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>22590</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>17402</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14184</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>15378</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4995; 15020</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5102; 14812</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2603; 10363</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1787; 8668</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8993; 19693</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5217; 14533</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4857; 13830</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>6474; 17300</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>16351; 30068</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12042; 25043</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9153; 21193</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>9647; 22309</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>19103</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16359</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22725</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17390</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24350</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>22599</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20105</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>14606</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>43454</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>38958</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>42830</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>31996</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>13301; 26924</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10375; 24500</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>15750; 30478</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>10069; 25693</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>17252; 31622</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>16239; 30947</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>14284; 27575</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>8958; 22575</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>34111; 53813</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>30318; 49958</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>33878; 53480</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>22953; 43497</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>12763</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16459</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9848</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15846</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5939</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17352</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11997</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>15923</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>18702</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>33811</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>21845</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>31769</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>8044; 19115</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>10530; 23321</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5830; 15812</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10801; 23703</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2728; 11135</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>11131; 24278</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7344; 18343</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>9607; 24893</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>12616; 26910</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>26560; 45314</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>15533; 29825</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>23590; 42923</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>12078</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9641</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6596</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3404</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4628</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>12436</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4534</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>13548</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>16706</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>22077</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>11130</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>16952</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>7748; 17564</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>5329; 14994</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3652; 12151</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1437; 6864</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2007; 9264</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>7757; 18988</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1793; 10310</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>7279; 20824</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>11145; 23992</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>16238; 30611</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>6408; 17616</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>10599; 24842</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>74440</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>69521</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>61985</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>58981</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>64099</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>80029</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>63369</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>82796</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>138539</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>149550</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>125354</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>141777</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>61988; 88865</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>56381; 82514</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>49984; 75554</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>46763; 73240</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>53050; 76743</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>66975; 94759</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>51149; 76085</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>68205; 99669</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>121070; 156692</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>130362; 168904</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>109329; 145069</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>122851; 162314</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP26C_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,57; 19,08</t>
+          <t>8,47; 19,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 12,14</t>
+          <t>2,94; 11,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 15,07</t>
+          <t>5,02; 15,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 13,24</t>
+          <t>4,51; 13,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 16,39</t>
+          <t>6,16; 16,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 15,7</t>
+          <t>5,68; 15,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,65; 14,16</t>
+          <t>4,8; 14,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,66; 20,37</t>
+          <t>8,49; 19,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,54; 15,83</t>
+          <t>8,52; 16,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 12,42</t>
+          <t>5,26; 12,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,95; 12,94</t>
+          <t>5,92; 12,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,12; 15,48</t>
+          <t>8,14; 15,46</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 16,15</t>
+          <t>5,25; 15,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,34; 20,02</t>
+          <t>8,75; 20,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 14,84</t>
+          <t>5,36; 14,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,13; 15,52</t>
+          <t>5,65; 15,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 11,42</t>
+          <t>3,02; 11,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 16,66</t>
+          <t>6,2; 16,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 14,35</t>
+          <t>4,6; 13,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 15,96</t>
+          <t>5,64; 15,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 11,5</t>
+          <t>5,14; 11,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,59; 16,16</t>
+          <t>8,6; 16,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 12,52</t>
+          <t>6,02; 12,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,68; 13,72</t>
+          <t>6,55; 13,71</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 22,52</t>
+          <t>7,74; 20,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 17,19</t>
+          <t>5,65; 16,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 16,76</t>
+          <t>4,08; 16,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 16,71</t>
+          <t>3,44; 17,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 19,83</t>
+          <t>8,69; 19,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 16,98</t>
+          <t>6,0; 16,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 18,49</t>
+          <t>6,31; 19,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,14; 27,09</t>
+          <t>9,72; 25,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,85; 18,11</t>
+          <t>9,81; 18,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 14,58</t>
+          <t>6,89; 14,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 15,51</t>
+          <t>6,69; 15,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,34; 19,28</t>
+          <t>8,71; 19,83</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 13,41</t>
+          <t>6,55; 13,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 11,97</t>
+          <t>5,26; 11,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 13,9</t>
+          <t>7,4; 14,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 11,79</t>
+          <t>4,74; 11,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,62; 15,8</t>
+          <t>8,71; 16,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 13,81</t>
+          <t>7,1; 13,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,84; 13,2</t>
+          <t>7,17; 13,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,34</t>
+          <t>4,34; 10,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,42</t>
+          <t>8,8; 13,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 11,65</t>
+          <t>7,04; 11,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 12,49</t>
+          <t>7,73; 12,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 9,97</t>
+          <t>5,38; 9,72</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 18,36</t>
+          <t>7,6; 18,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 15,89</t>
+          <t>7,38; 16,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,3; 11,66</t>
+          <t>4,18; 11,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,04; 19,85</t>
+          <t>8,9; 19,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,89</t>
+          <t>2,2; 9,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,96; 17,37</t>
+          <t>8,28; 17,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 12,91</t>
+          <t>5,24; 13,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 15,31</t>
+          <t>6,24; 15,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 11,73</t>
+          <t>5,47; 11,54</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,27; 15,81</t>
+          <t>8,84; 15,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,59; 10,74</t>
+          <t>5,42; 10,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,36; 15,22</t>
+          <t>8,15; 15,27</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,35; 23,46</t>
+          <t>10,28; 23,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,02; 28,2</t>
+          <t>10,79; 29,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,98; 19,89</t>
+          <t>5,82; 20,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 9,96</t>
+          <t>2,31; 10,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,8; 12,91</t>
+          <t>2,74; 12,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,57; 25,87</t>
+          <t>10,02; 25,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 15,51</t>
+          <t>3,19; 13,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,11; 28,92</t>
+          <t>10,49; 28,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,6; 16,36</t>
+          <t>7,53; 16,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,83; 24,18</t>
+          <t>12,74; 24,12</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,02; 13,81</t>
+          <t>5,18; 13,48</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,52; 17,63</t>
+          <t>7,7; 17,95</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,73; 13,95</t>
+          <t>9,84; 13,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,3</t>
+          <t>8,64; 12,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 11,37</t>
+          <t>7,7; 11,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,16</t>
+          <t>7,17; 10,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,81; 11,3</t>
+          <t>7,78; 11,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,46; 13,38</t>
+          <t>9,33; 13,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 10,82</t>
+          <t>7,37; 10,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,1; 13,3</t>
+          <t>8,93; 13,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,2; 11,91</t>
+          <t>9,17; 11,88</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,45; 12,25</t>
+          <t>9,49; 12,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,99; 10,6</t>
+          <t>7,89; 10,44</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,74; 11,55</t>
+          <t>8,72; 11,58</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8882; 19782</t>
+          <t>8784; 20491</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2816; 10696</t>
+          <t>2589; 10390</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4305; 12410</t>
+          <t>4139; 12668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4812; 13670</t>
+          <t>4662; 13671</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5936; 15985</t>
+          <t>6009; 15885</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5145; 13997</t>
+          <t>5061; 13587</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4644; 14129</t>
+          <t>4789; 14135</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11852; 27891</t>
+          <t>11629; 26051</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17191; 31848</t>
+          <t>17136; 33084</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9494; 22010</t>
+          <t>9324; 21390</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10845; 23577</t>
+          <t>10779; 23399</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19493; 37173</t>
+          <t>19541; 37138</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4281; 14017</t>
+          <t>4553; 13287</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7652; 18381</t>
+          <t>8029; 19219</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6091; 15503</t>
+          <t>5602; 15210</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4858; 14699</t>
+          <t>5345; 14749</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2585; 9740</t>
+          <t>2579; 9486</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5555; 16018</t>
+          <t>5961; 16218</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5432; 15989</t>
+          <t>5122; 15269</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5190; 15252</t>
+          <t>5386; 14808</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8370; 19792</t>
+          <t>8838; 19965</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16142; 30375</t>
+          <t>16158; 30663</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13303; 27035</t>
+          <t>12985; 26522</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12708; 26103</t>
+          <t>12461; 26084</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4995; 15020</t>
+          <t>5161; 13919</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5102; 14812</t>
+          <t>4869; 14509</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2603; 10363</t>
+          <t>2524; 9894</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1787; 8668</t>
+          <t>1783; 9129</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8993; 19693</t>
+          <t>8631; 19233</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5217; 14533</t>
+          <t>5139; 14104</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4857; 13830</t>
+          <t>4719; 14756</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6474; 17300</t>
+          <t>6205; 16481</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16351; 30068</t>
+          <t>16287; 30542</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12042; 25043</t>
+          <t>11835; 25181</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9153; 21193</t>
+          <t>9134; 21012</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9647; 22309</t>
+          <t>10075; 22942</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13301; 26924</t>
+          <t>13140; 26141</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10375; 24500</t>
+          <t>10768; 24494</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15750; 30478</t>
+          <t>16222; 31177</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10069; 25693</t>
+          <t>10341; 25639</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17252; 31622</t>
+          <t>17436; 32496</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16239; 30947</t>
+          <t>15905; 30817</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14284; 27575</t>
+          <t>14969; 28325</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8958; 22575</t>
+          <t>9478; 21907</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34111; 53813</t>
+          <t>35281; 54473</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30318; 49958</t>
+          <t>30198; 49175</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33878; 53480</t>
+          <t>33113; 52904</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22953; 43497</t>
+          <t>23474; 42393</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8044; 19115</t>
+          <t>7914; 19688</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10530; 23321</t>
+          <t>10833; 24386</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5830; 15812</t>
+          <t>5675; 16262</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10801; 23703</t>
+          <t>10626; 23181</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2728; 11135</t>
+          <t>2751; 11628</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11131; 24278</t>
+          <t>11574; 24422</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7344; 18343</t>
+          <t>7450; 18511</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9607; 24893</t>
+          <t>10149; 25058</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12616; 26910</t>
+          <t>12547; 26469</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26560; 45314</t>
+          <t>25324; 43054</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15533; 29825</t>
+          <t>15048; 29599</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23590; 42923</t>
+          <t>22976; 43072</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7748; 17564</t>
+          <t>7700; 17908</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5329; 14994</t>
+          <t>5738; 15635</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3652; 12151</t>
+          <t>3553; 12437</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1437; 6864</t>
+          <t>1590; 7020</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2007; 9264</t>
+          <t>1969; 9284</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7757; 18988</t>
+          <t>7358; 18387</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1793; 10310</t>
+          <t>2123; 8934</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7279; 20824</t>
+          <t>7553; 20377</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11145; 23992</t>
+          <t>11038; 23830</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16238; 30611</t>
+          <t>16131; 30537</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6408; 17616</t>
+          <t>6613; 17195</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10599; 24842</t>
+          <t>10853; 25286</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>61988; 88865</t>
+          <t>62679; 88342</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>56381; 82514</t>
+          <t>57984; 84740</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49984; 75554</t>
+          <t>51200; 74894</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46763; 73240</t>
+          <t>47061; 71917</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>53050; 76743</t>
+          <t>52880; 76195</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66975; 94759</t>
+          <t>66099; 93379</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51149; 76085</t>
+          <t>51876; 76703</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>68205; 99669</t>
+          <t>66933; 97390</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>121070; 156692</t>
+          <t>120642; 156378</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>130362; 168904</t>
+          <t>130854; 169797</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109329; 145069</t>
+          <t>107931; 142767</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>122851; 162314</t>
+          <t>122498; 162693</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP26C_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10,41%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14,09%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>12,9%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,4%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9,35%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,41%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,47; 19,76</t>
+          <t>6,45; 16,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 11,8</t>
+          <t>5,45; 15,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 15,38</t>
+          <t>4,73; 14,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 13,24</t>
+          <t>9,09; 21,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 16,28</t>
+          <t>8,31; 18,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 15,24</t>
+          <t>3,05; 12,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 14,16</t>
+          <t>5,24; 15,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,49; 19,03</t>
+          <t>5,05; 13,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,52; 16,44</t>
+          <t>8,25; 15,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 12,07</t>
+          <t>5,24; 12,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 12,85</t>
+          <t>6,1; 12,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 15,46</t>
+          <t>8,2; 16,1</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,39%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>9,55%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>13,76%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>9,3%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,72%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 15,31</t>
+          <t>3,0; 11,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,75; 20,94</t>
+          <t>6,26; 16,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,36; 14,56</t>
+          <t>4,53; 14,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 15,58</t>
+          <t>5,27; 16,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 11,12</t>
+          <t>5,03; 15,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 16,87</t>
+          <t>8,53; 20,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 13,71</t>
+          <t>5,2; 14,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 15,49</t>
+          <t>5,42; 15,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,14; 11,6</t>
+          <t>4,89; 12,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 16,32</t>
+          <t>8,49; 16,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 12,29</t>
+          <t>5,96; 12,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 13,71</t>
+          <t>6,89; 14,37</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,75%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18,37%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>13,25%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10,21%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>8,72%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,75%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 20,87</t>
+          <t>8,55; 20,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 16,84</t>
+          <t>5,39; 15,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 16,0</t>
+          <t>5,92; 18,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 17,6</t>
+          <t>11,15; 29,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 19,36</t>
+          <t>7,68; 21,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 16,48</t>
+          <t>5,86; 17,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 19,73</t>
+          <t>4,1; 16,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,72; 25,81</t>
+          <t>4,02; 16,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,81; 18,4</t>
+          <t>9,72; 18,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 14,66</t>
+          <t>6,49; 14,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 15,38</t>
+          <t>6,46; 14,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,71; 19,83</t>
+          <t>8,71; 20,24</t>
         </is>
       </c>
     </row>
@@ -1069,44 +1069,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,63%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,52%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,99%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10,36%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,17%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9,63%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10,84%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 13,02</t>
+          <t>8,79; 16,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 11,96</t>
+          <t>7,21; 14,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 14,22</t>
+          <t>6,38; 13,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 11,76</t>
+          <t>4,25; 10,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 16,24</t>
+          <t>6,34; 12,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 13,75</t>
+          <t>5,08; 11,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 13,56</t>
+          <t>7,54; 14,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 10,04</t>
+          <t>6,49; 13,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 13,59</t>
+          <t>8,69; 13,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 11,47</t>
+          <t>7,01; 11,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,36</t>
+          <t>7,76; 12,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,72</t>
+          <t>6,11; 11,04</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12,42%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>12,26%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>11,21%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>7,26%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13,27%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,42%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,6; 18,91</t>
+          <t>2,18; 8,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,38; 16,61</t>
+          <t>8,69; 17,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 11,99</t>
+          <t>5,23; 13,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,9; 19,41</t>
+          <t>6,28; 16,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,28</t>
+          <t>7,54; 19,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,28; 17,47</t>
+          <t>7,44; 16,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 13,03</t>
+          <t>4,33; 11,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 15,41</t>
+          <t>9,09; 20,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 11,54</t>
+          <t>5,4; 11,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 15,03</t>
+          <t>9,13; 15,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 10,66</t>
+          <t>5,87; 11,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 15,27</t>
+          <t>8,89; 16,33</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16,94%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17,92%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>16,13%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>18,13%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>10,8%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,28; 23,92</t>
+          <t>2,85; 12,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,79; 29,4</t>
+          <t>10,05; 25,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,82; 20,36</t>
+          <t>3,19; 13,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,31; 10,19</t>
+          <t>10,51; 27,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,74; 12,94</t>
+          <t>10,14; 23,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,02; 25,05</t>
+          <t>10,77; 28,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 13,44</t>
+          <t>5,37; 18,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,49; 28,3</t>
+          <t>2,1; 9,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,53; 16,25</t>
+          <t>7,76; 16,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,74; 24,12</t>
+          <t>12,78; 23,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,48</t>
+          <t>4,71; 13,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,7; 17,95</t>
+          <t>7,15; 16,39</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9,44%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9,01%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>11,69%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>10,36%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>9,33%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,84; 13,87</t>
+          <t>7,86; 11,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,64; 12,63</t>
+          <t>9,37; 13,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,7; 11,27</t>
+          <t>7,34; 10,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,17; 10,96</t>
+          <t>9,6; 13,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,78; 11,22</t>
+          <t>9,57; 13,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,33; 13,19</t>
+          <t>8,59; 12,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,9</t>
+          <t>7,6; 11,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,93; 13,0</t>
+          <t>7,92; 11,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,17; 11,88</t>
+          <t>9,17; 11,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,49; 12,31</t>
+          <t>9,4; 12,28</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,89; 10,44</t>
+          <t>7,84; 10,54</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,72; 11,58</t>
+          <t>9,37; 12,19</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10152</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8700</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8592</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17268</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>13374</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>5634</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>7703</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8656</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10152</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8700</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8592</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27216</t>
+          <t>26087</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8784; 20491</t>
+          <t>6296; 15645</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2589; 10390</t>
+          <t>4855; 13954</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4139; 12668</t>
+          <t>4722; 14867</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4662; 13671</t>
+          <t>11139; 26431</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6009; 15885</t>
+          <t>8619; 19521</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5061; 13587</t>
+          <t>2685; 10668</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4789; 14135</t>
+          <t>4319; 12562</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11629; 26051</t>
+          <t>5138; 13978</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17136; 33084</t>
+          <t>16610; 31701</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9324; 21390</t>
+          <t>9295; 21996</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10779; 23399</t>
+          <t>11110; 23338</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19541; 37138</t>
+          <t>18382; 36120</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5276</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10340</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9353</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9258</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8285</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12628</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9718</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9207</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5276</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10340</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9353</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>9396</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18466</t>
+          <t>18654</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4553; 13287</t>
+          <t>2561; 9752</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8029; 19219</t>
+          <t>6021; 15897</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5602; 15210</t>
+          <t>5045; 15660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5345; 14749</t>
+          <t>4814; 15221</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2579; 9486</t>
+          <t>4367; 13568</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5961; 16218</t>
+          <t>7827; 18732</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5122; 15269</t>
+          <t>5432; 15278</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5386; 14808</t>
+          <t>5230; 15422</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8838; 19965</t>
+          <t>8407; 20719</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16158; 30663</t>
+          <t>15947; 31146</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12985; 26522</t>
+          <t>12873; 26422</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12461; 26084</t>
+          <t>12951; 27006</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13754</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8602</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8789</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10457</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>8837</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>8800</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>5395</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4476</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13754</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8602</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8789</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15378</t>
+          <t>15131</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5161; 13919</t>
+          <t>8491; 20055</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4869; 14509</t>
+          <t>4613; 13524</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2524; 9894</t>
+          <t>4428; 13792</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1783; 9129</t>
+          <t>6350; 16824</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8631; 19233</t>
+          <t>5124; 14040</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5139; 14104</t>
+          <t>5052; 14656</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4719; 14756</t>
+          <t>2533; 9952</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6205; 16481</t>
+          <t>2151; 9052</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16287; 30542</t>
+          <t>16132; 30247</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11835; 25181</t>
+          <t>11150; 24249</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9134; 21012</t>
+          <t>8830; 20418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10075; 22942</t>
+          <t>9617; 22351</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24350</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22599</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20105</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14245</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>19103</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>16359</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>22725</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17390</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24350</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22599</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20105</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31996</t>
+          <t>31462</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13140; 26141</t>
+          <t>17588; 32217</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10768; 24494</t>
+          <t>16148; 31892</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16222; 31177</t>
+          <t>13332; 27205</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10341; 25639</t>
+          <t>8576; 22088</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17436; 32496</t>
+          <t>12731; 25977</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15905; 30817</t>
+          <t>10391; 23690</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14969; 28325</t>
+          <t>16536; 31436</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9478; 21907</t>
+          <t>11599; 23948</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35281; 54473</t>
+          <t>34835; 55159</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30198; 49175</t>
+          <t>30070; 48694</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33113; 52904</t>
+          <t>33225; 53345</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23474; 42393</t>
+          <t>23265; 42027</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5939</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17352</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11997</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15648</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>12763</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>16459</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>9848</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>15846</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>5939</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17352</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11997</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15923</t>
+          <t>16697</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31769</t>
+          <t>32345</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7914; 19688</t>
+          <t>2726; 10697</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10833; 24386</t>
+          <t>12149; 24533</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5675; 16262</t>
+          <t>7435; 18836</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10626; 23181</t>
+          <t>9303; 24241</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2751; 11628</t>
+          <t>7847; 20089</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11574; 24422</t>
+          <t>10922; 24049</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7450; 18511</t>
+          <t>5871; 16175</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10149; 25058</t>
+          <t>10795; 23832</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12547; 26469</t>
+          <t>12379; 25819</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25324; 43054</t>
+          <t>26159; 43140</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15048; 29599</t>
+          <t>16304; 30666</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22976; 43072</t>
+          <t>23723; 43606</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4628</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12436</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4534</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12240</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>12078</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>9641</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>6596</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3404</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4628</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>12436</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4534</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16952</t>
+          <t>15446</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7700; 17908</t>
+          <t>2043; 9222</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5738; 15635</t>
+          <t>7381; 18393</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3553; 12437</t>
+          <t>2120; 9179</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1590; 7020</t>
+          <t>7180; 18762</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1969; 9284</t>
+          <t>7595; 17705</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7358; 18387</t>
+          <t>5729; 14985</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2123; 8934</t>
+          <t>3280; 11496</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7553; 20377</t>
+          <t>1476; 6812</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11038; 23830</t>
+          <t>11370; 23948</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16131; 30537</t>
+          <t>16181; 30021</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6613; 17195</t>
+          <t>6003; 16894</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10853; 25286</t>
+          <t>9908; 22729</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>64099</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>80029</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>63369</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>79116</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>74440</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>69521</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>61985</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>58981</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>64099</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>80029</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>63369</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>60010</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>141777</t>
+          <t>139125</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>62679; 88342</t>
+          <t>53424; 78673</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>57984; 84740</t>
+          <t>66366; 94788</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51200; 74894</t>
+          <t>51624; 76989</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47061; 71917</t>
+          <t>66201; 95755</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>52880; 76195</t>
+          <t>60953; 87832</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66099; 93379</t>
+          <t>57593; 82637</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51876; 76703</t>
+          <t>50518; 75644</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>66933; 97390</t>
+          <t>49060; 73190</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>120642; 156378</t>
+          <t>120625; 155693</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>130854; 169797</t>
+          <t>129576; 169331</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>107931; 142767</t>
+          <t>107313; 144214</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>122498; 162693</t>
+          <t>122643; 159547</t>
         </is>
       </c>
     </row>
